--- a/סוגי_נכסים_20251216.xlsx
+++ b/סוגי_נכסים_20251216.xlsx
@@ -409,7 +409,7 @@
     <col min="8" max="8" width="40.83203125" customWidth="1"/>
     <col min="9" max="9" width="15.83203125" customWidth="1"/>
     <col min="10" max="10" width="20.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" customWidth="1"/>
     <col min="12" max="12" width="15.83203125" customWidth="1"/>
     <col min="13" max="13" width="10.83203125" customWidth="1"/>
     <col min="14" max="14" width="10.83203125" customWidth="1"/>
@@ -450,7 +450,7 @@
         <v>שימוש בשטח משותף</v>
       </c>
       <c r="L1" t="str">
-        <v>לא נספר</v>
+        <v>לא נספר בחישוב שטח מבנה</v>
       </c>
       <c r="M1" t="str">
         <v>שטח מ</v>
@@ -7967,7 +7967,7 @@
         <v/>
       </c>
       <c r="L161" t="str">
-        <v>לא</v>
+        <v>כן</v>
       </c>
       <c r="M161" t="str">
         <v>כן</v>
